--- a/output/pdf_financials_xlsx/VML.xlsx
+++ b/output/pdf_financials_xlsx/VML.xlsx
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.073092</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.387532</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.877776</v>
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
@@ -5896,13 +5896,13 @@
         </is>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.729134</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.580314</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.56465</v>
       </c>
     </row>
     <row r="93">
@@ -7435,16 +7435,16 @@
         </is>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-1.454908</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.381423</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.325384</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-1.674811</v>
       </c>
     </row>
     <row r="119">
@@ -9498,7 +9498,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -9998,7 +10002,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -10920,7 +10928,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -12108,7 +12120,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -13658,7 +13674,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VML.xlsx
+++ b/output/pdf_financials_xlsx/VML.xlsx
@@ -865,22 +865,22 @@
         <v>1.503092</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.6503910000000001</v>
+        <v>1.488887</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.76889</v>
+        <v>1.636098</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.650999</v>
+        <v>1.344381</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.564658</v>
+        <v>1.077203</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.07849200000000001</v>
+        <v>2.012854</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.184339</v>
+        <v>1.835478</v>
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
@@ -916,22 +916,22 @@
         <v>-1.503092</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.6503910000000001</v>
+        <v>-1.488887</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.76889</v>
+        <v>-1.636098</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.650999</v>
+        <v>-1.344381</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.564658</v>
+        <v>-1.077203</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.07849200000000001</v>
+        <v>-2.012854</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.184339</v>
+        <v>-1.835478</v>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
@@ -958,22 +958,22 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000213</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>6.4e-05</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.00067</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000266</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.005285</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000199</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -982,7 +982,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.006745</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
@@ -990,13 +990,13 @@
         </is>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.004525</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.002003</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.043203</v>
       </c>
     </row>
     <row r="13">
@@ -1777,22 +1777,22 @@
         <v>-0.387112</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.080745</v>
+        <v>-1.080958</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.121458</v>
+        <v>-1.121522</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.504307</v>
+        <v>-1.504977</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.448803</v>
+        <v>-1.449069</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.636098</v>
+        <v>-1.641383</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.340986</v>
+        <v>-1.341185</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-1.097812</v>
@@ -1801,7 +1801,7 @@
         <v>-2.012854</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.733533</v>
+        <v>-1.740278</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -1809,13 +1809,13 @@
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.696171</v>
+        <v>-1.700696</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.112792</v>
+        <v>-1.114795</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.594565</v>
+        <v>-1.637768</v>
       </c>
     </row>
     <row r="28">
@@ -1879,22 +1879,22 @@
         <v>-0.387112</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.080745</v>
+        <v>-1.080958</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.121458</v>
+        <v>-1.121522</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.504307</v>
+        <v>-1.504977</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.448803</v>
+        <v>-1.449069</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.636098</v>
+        <v>-1.641383</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.340986</v>
+        <v>-1.341185</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-1.097812</v>
@@ -1903,7 +1903,7 @@
         <v>-2.012854</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.733533</v>
+        <v>-1.740278</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.696171</v>
+        <v>-1.700696</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.112792</v>
+        <v>-1.114795</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.594565</v>
+        <v>-1.637768</v>
       </c>
     </row>
     <row r="30">
@@ -18006,7 +18006,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -18542,7 +18542,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -19134,7 +19134,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -19954,7 +19954,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -19978,22 +19978,22 @@
         </is>
       </c>
       <c r="I136" s="5" t="n">
-        <v>-1.488887</v>
+        <v>1.488887</v>
       </c>
       <c r="J136" s="5" t="n">
-        <v>-1.636098</v>
+        <v>1.636098</v>
       </c>
       <c r="K136" s="5" t="n">
-        <v>-1.344381</v>
+        <v>1.344381</v>
       </c>
       <c r="L136" s="5" t="n">
-        <v>-1.077203</v>
+        <v>1.077203</v>
       </c>
       <c r="M136" s="5" t="n">
-        <v>-2.012854</v>
+        <v>2.012854</v>
       </c>
       <c r="N136" s="5" t="n">
-        <v>-1.835478</v>
+        <v>1.835478</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -22164,7 +22164,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -23346,7 +23346,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
